--- a/PlayGround/Verification Freq_Metrics low_constraints/batch_results.xlsx
+++ b/PlayGround/Verification Freq_Metrics low_constraints/batch_results.xlsx
@@ -494,16 +494,16 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>3.118086721304095</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07109581863690263</v>
+        <v>0.07819006800684319</v>
       </c>
       <c r="H2" t="n">
-        <v>93.89157135753747</v>
+        <v>56.27109567976501</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.9999999943207097</v>
+        <v>1.090602053416904</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -533,19 +533,19 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9.998604187291207</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.99239610730252</v>
+        <v>1.982910821229395</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03041755473293923</v>
+        <v>0.03012929436453698</v>
       </c>
       <c r="H3" t="n">
-        <v>92.84862391492489</v>
+        <v>92.83442229922181</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9999999945033734</v>
+        <v>0.9999999945043093</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -578,16 +578,16 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>1.27746759999193</v>
+        <v>1.278053777602519</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01380102902752884</v>
+        <v>0.01374002847187117</v>
       </c>
       <c r="H4" t="n">
-        <v>91.23715495370159</v>
+        <v>91.23920716012289</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.9999999947827988</v>
+        <v>0.9999999947824397</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -620,16 +620,16 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9975722323271083</v>
+        <v>0.9998713609668319</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01012176056726889</v>
+        <v>0.009981129755320371</v>
       </c>
       <c r="H5" t="n">
-        <v>89.98619252953175</v>
+        <v>89.99927003906453</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.9999999950024338</v>
+        <v>0.9999999950001287</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -659,19 +659,19 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9.999976516340251</v>
       </c>
       <c r="E6" t="n">
-        <v>9.630918958985848</v>
+        <v>9.593753349802112</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3165634337185056</v>
+        <v>0.3059266972573095</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5915653867346087</v>
+        <v>0.5903456723861441</v>
       </c>
       <c r="H6" t="n">
-        <v>77.78336446782758</v>
+        <v>76.83838800813773</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.02937054845866</v>
+        <v>1.029035404593996</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -704,16 +704,16 @@
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>7.324023290823163</v>
+        <v>7.311540059318117</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3033581797903072</v>
+        <v>0.3012144765959506</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3620639610069521</v>
+        <v>0.3624870578589331</v>
       </c>
       <c r="H7" t="n">
-        <v>76.38478531793979</v>
+        <v>76.18380062012416</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.02897713428263</v>
+        <v>1.028928750946039</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -743,19 +743,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>9.997010762600993</v>
+        <v>9.933081526254629</v>
       </c>
       <c r="E8" t="n">
-        <v>5.584261410479423</v>
+        <v>5.606330791609965</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2953967652375804</v>
+        <v>0.301915419709734</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2388612525349979</v>
+        <v>0.2383165946990712</v>
       </c>
       <c r="H8" t="n">
-        <v>75.32499458148847</v>
+        <v>75.95910914819412</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.02884454556188</v>
+        <v>1.028798944527327</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -788,16 +788,16 @@
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>4.638902492759621</v>
+        <v>4.663498421445201</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2887116011481838</v>
+        <v>0.2909419744511686</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1877918006576312</v>
+        <v>0.1872614160114804</v>
       </c>
       <c r="H9" t="n">
-        <v>74.37576253152984</v>
+        <v>74.61211645564259</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.028867677600202</v>
+        <v>1.02884824608522</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -827,25 +827,25 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5.042173472877457</v>
+        <v>5.605304115638497</v>
       </c>
       <c r="E10" t="n">
-        <v>8.768791553518</v>
+        <v>9.7538102559721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7021283806104488</v>
+        <v>0.6975779473914325</v>
       </c>
       <c r="G10" t="n">
-        <v>1.871422016624041</v>
+        <v>1.865658857247324</v>
       </c>
       <c r="H10" t="n">
-        <v>49.26392792667303</v>
+        <v>46.39037483945626</v>
       </c>
       <c r="I10" t="n">
-        <v>33.08197523052989</v>
+        <v>32.16884640743183</v>
       </c>
       <c r="J10" t="n">
-        <v>1.578321278738765</v>
+        <v>1.634628835737352</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -867,25 +867,25 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>6.936306911663003</v>
+        <v>6.953631304898193</v>
       </c>
       <c r="E11" t="n">
-        <v>9.98795456877043</v>
+        <v>9.996998039894875</v>
       </c>
       <c r="F11" t="n">
-        <v>0.707626500936288</v>
+        <v>0.7044425155107971</v>
       </c>
       <c r="G11" t="n">
-        <v>1.343757908317622</v>
+        <v>1.343304146520534</v>
       </c>
       <c r="H11" t="n">
-        <v>41.32448306970289</v>
+        <v>41.21500425837397</v>
       </c>
       <c r="I11" t="n">
-        <v>30.30547747097404</v>
+        <v>30.28806701208214</v>
       </c>
       <c r="J11" t="n">
-        <v>1.753730773099449</v>
+        <v>1.75710774820103</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -907,25 +907,25 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>8.372810398195201</v>
+        <v>8.412948738062683</v>
       </c>
       <c r="E12" t="n">
-        <v>9.917150607514154</v>
+        <v>9.973690460917869</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7139423724299289</v>
+        <v>0.7149335658052648</v>
       </c>
       <c r="G12" t="n">
-        <v>1.005784746332927</v>
+        <v>1.005660939388232</v>
       </c>
       <c r="H12" t="n">
-        <v>37.26040461964007</v>
+        <v>37.17681851806</v>
       </c>
       <c r="I12" t="n">
-        <v>28.66175368538828</v>
+        <v>28.61882350580224</v>
       </c>
       <c r="J12" t="n">
-        <v>1.878919815536071</v>
+        <v>1.881173674585738</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -947,25 +947,25 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9.998897648261599</v>
       </c>
       <c r="E13" t="n">
-        <v>9.910417296762363</v>
+        <v>9.93304130103864</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7197971531760886</v>
+        <v>0.7224394815779344</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8030701128035322</v>
+        <v>0.8037490993142375</v>
       </c>
       <c r="H13" t="n">
-        <v>33.77530174997239</v>
+        <v>33.81312212179088</v>
       </c>
       <c r="I13" t="n">
-        <v>27.11055962651041</v>
+        <v>27.10750940884129</v>
       </c>
       <c r="J13" t="n">
-        <v>2.014854140569761</v>
+        <v>2.012800700397146</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -987,25 +987,25 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1.924034060487793</v>
+        <v>1.925995834695637</v>
       </c>
       <c r="E14" t="n">
-        <v>5.060718204576247</v>
+        <v>5.067909394028937</v>
       </c>
       <c r="F14" t="n">
-        <v>1.109472952468987</v>
+        <v>1.109244636247119</v>
       </c>
       <c r="G14" t="n">
-        <v>4.709167287621996</v>
+        <v>4.709118388326361</v>
       </c>
       <c r="H14" t="n">
-        <v>68.18383994030887</v>
+        <v>68.12135289035371</v>
       </c>
       <c r="I14" t="n">
-        <v>12.08910969904702</v>
+        <v>12.08033632702556</v>
       </c>
       <c r="J14" t="n">
-        <v>1.646516313900076</v>
+        <v>1.647365914456673</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1027,25 +1027,25 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2.31323136188172</v>
+        <v>2.301597773453467</v>
       </c>
       <c r="E15" t="n">
-        <v>5.668362502589867</v>
+        <v>5.655284594905273</v>
       </c>
       <c r="F15" t="n">
-        <v>1.17384364254715</v>
+        <v>1.174175232987934</v>
       </c>
       <c r="G15" t="n">
-        <v>4.493745260966898</v>
+        <v>4.493516396411684</v>
       </c>
       <c r="H15" t="n">
-        <v>56.7020000972919</v>
+        <v>57.02886255117539</v>
       </c>
       <c r="I15" t="n">
-        <v>10.43389716162991</v>
+        <v>10.4774545233032</v>
       </c>
       <c r="J15" t="n">
-        <v>1.836792788780124</v>
+        <v>1.830785533622615</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1067,25 +1067,25 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.286519756859314</v>
+        <v>2.287275036847099</v>
       </c>
       <c r="E16" t="n">
-        <v>5.543018394497465</v>
+        <v>5.542300881031102</v>
       </c>
       <c r="F16" t="n">
-        <v>1.167593944596218</v>
+        <v>1.166328946959347</v>
       </c>
       <c r="G16" t="n">
-        <v>4.39496427198735</v>
+        <v>4.39504856321201</v>
       </c>
       <c r="H16" t="n">
-        <v>57.42090027025687</v>
+        <v>57.39455791540864</v>
       </c>
       <c r="I16" t="n">
-        <v>10.54201096495017</v>
+        <v>10.54039013684545</v>
       </c>
       <c r="J16" t="n">
-        <v>1.822216773776717</v>
+        <v>1.822482614099115</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1107,25 +1107,25 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>2.260368485858385</v>
+        <v>2.251221876704462</v>
       </c>
       <c r="E17" t="n">
-        <v>5.33962257625654</v>
+        <v>5.311741799020101</v>
       </c>
       <c r="F17" t="n">
-        <v>1.158836814704154</v>
+        <v>1.154094633426771</v>
       </c>
       <c r="G17" t="n">
-        <v>4.213323922167082</v>
+        <v>4.212935565290714</v>
       </c>
       <c r="H17" t="n">
-        <v>58.09235636685075</v>
+        <v>58.32257613733212</v>
       </c>
       <c r="I17" t="n">
-        <v>10.65194075070499</v>
+        <v>10.69176567107803</v>
       </c>
       <c r="J17" t="n">
-        <v>1.807269866685011</v>
+        <v>1.801847204288627</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1147,25 +1147,25 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1.423094601041595</v>
+        <v>1.430429702214439</v>
       </c>
       <c r="E18" t="n">
-        <v>5.268139446055719</v>
+        <v>5.292633330622758</v>
       </c>
       <c r="F18" t="n">
-        <v>1.461062131779466</v>
+        <v>1.464673821953689</v>
       </c>
       <c r="G18" t="n">
-        <v>9.825937438010635</v>
+        <v>9.826436581968077</v>
       </c>
       <c r="H18" t="n">
-        <v>77.90505881884044</v>
+        <v>77.73859992360633</v>
       </c>
       <c r="I18" t="n">
-        <v>8.662712912751427</v>
+        <v>8.611993160904035</v>
       </c>
       <c r="J18" t="n">
-        <v>1.796280427550613</v>
+        <v>1.803405085641472</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1187,25 +1187,25 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>1.419150921946048</v>
+        <v>1.423345241908586</v>
       </c>
       <c r="E19" t="n">
-        <v>5.216647222312241</v>
+        <v>5.215673508553283</v>
       </c>
       <c r="F19" t="n">
-        <v>1.453466150021317</v>
+        <v>1.451831821003704</v>
       </c>
       <c r="G19" t="n">
-        <v>9.700222183690581</v>
+        <v>9.700669815274555</v>
       </c>
       <c r="H19" t="n">
-        <v>77.69452758303561</v>
+        <v>77.4613919581665</v>
       </c>
       <c r="I19" t="n">
-        <v>8.699197182634471</v>
+        <v>8.675667754854292</v>
       </c>
       <c r="J19" t="n">
-        <v>1.791462057536204</v>
+        <v>1.794957339120998</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1227,25 +1227,25 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.421390524267048</v>
+        <v>1.420438813209667</v>
       </c>
       <c r="E20" t="n">
-        <v>5.146681492898942</v>
+        <v>5.138358042133236</v>
       </c>
       <c r="F20" t="n">
-        <v>1.440480811507592</v>
+        <v>1.447334006398513</v>
       </c>
       <c r="G20" t="n">
-        <v>9.49591117580851</v>
+        <v>9.495886621892765</v>
       </c>
       <c r="H20" t="n">
-        <v>76.9798135286008</v>
+        <v>77.12095052510416</v>
       </c>
       <c r="I20" t="n">
-        <v>8.704379346387203</v>
+        <v>8.702078692994272</v>
       </c>
       <c r="J20" t="n">
-        <v>1.791183327974425</v>
+        <v>1.791257623422544</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -1267,25 +1267,25 @@
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>1.413173192054885</v>
+        <v>1.405479927315045</v>
       </c>
       <c r="E21" t="n">
-        <v>4.996342655999588</v>
+        <v>4.985628387435495</v>
       </c>
       <c r="F21" t="n">
-        <v>1.431992776274</v>
+        <v>1.427833340156758</v>
       </c>
       <c r="G21" t="n">
-        <v>9.09918455596071</v>
+        <v>9.099186575887677</v>
       </c>
       <c r="H21" t="n">
-        <v>76.33694743897556</v>
+        <v>76.49494682774275</v>
       </c>
       <c r="I21" t="n">
-        <v>8.770857701653814</v>
+        <v>8.82358565575711</v>
       </c>
       <c r="J21" t="n">
-        <v>1.781553354040741</v>
+        <v>1.774027185926198</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -1307,25 +1307,25 @@
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1.041441863309942</v>
+        <v>1.041060754061351</v>
       </c>
       <c r="E22" t="n">
-        <v>5.153871494177079</v>
+        <v>5.151402858090703</v>
       </c>
       <c r="F22" t="n">
-        <v>1.65008092364586</v>
+        <v>1.656051186839413</v>
       </c>
       <c r="G22" t="n">
-        <v>16.60264446261599</v>
+        <v>16.6028173495072</v>
       </c>
       <c r="H22" t="n">
-        <v>77.75096132326904</v>
+        <v>77.80946983743232</v>
       </c>
       <c r="I22" t="n">
-        <v>8.610803826830901</v>
+        <v>8.607487842946975</v>
       </c>
       <c r="J22" t="n">
-        <v>1.705456182937406</v>
+        <v>1.70573443664666</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -1347,25 +1347,25 @@
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>1.037066530770311</v>
+        <v>1.041948736428216</v>
       </c>
       <c r="E23" t="n">
-        <v>5.111605876496255</v>
+        <v>5.118201301710092</v>
       </c>
       <c r="F23" t="n">
-        <v>1.640626592409259</v>
+        <v>1.646378006526998</v>
       </c>
       <c r="G23" t="n">
-        <v>16.40344943237574</v>
+        <v>16.40279588211311</v>
       </c>
       <c r="H23" t="n">
-        <v>77.33662932868387</v>
+        <v>77.36890304306716</v>
       </c>
       <c r="I23" t="n">
-        <v>8.660571667417789</v>
+        <v>8.613087236523272</v>
       </c>
       <c r="J23" t="n">
-        <v>1.699118302463122</v>
+        <v>1.705202428915805</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -1387,25 +1387,25 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.043124230373465</v>
+        <v>1.044186210118708</v>
       </c>
       <c r="E24" t="n">
-        <v>5.070030372462905</v>
+        <v>5.074324361564709</v>
       </c>
       <c r="F24" t="n">
-        <v>1.635057527712561</v>
+        <v>1.632808633797747</v>
       </c>
       <c r="G24" t="n">
-        <v>16.06740095497004</v>
+        <v>16.06797577395913</v>
       </c>
       <c r="H24" t="n">
-        <v>76.75896076690867</v>
+        <v>76.74746854159872</v>
       </c>
       <c r="I24" t="n">
-        <v>8.618725416130305</v>
+        <v>8.611966022434936</v>
       </c>
       <c r="J24" t="n">
-        <v>1.704577140595136</v>
+        <v>1.705497615195222</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -1427,25 +1427,25 @@
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>1.040579348057006</v>
+        <v>1.037365982151303</v>
       </c>
       <c r="E25" t="n">
-        <v>4.941050433224221</v>
+        <v>4.935152825173581</v>
       </c>
       <c r="F25" t="n">
-        <v>1.623561385335571</v>
+        <v>1.615049060299762</v>
       </c>
       <c r="G25" t="n">
-        <v>15.40741611363795</v>
+        <v>15.40709064832585</v>
       </c>
       <c r="H25" t="n">
-        <v>75.43374327038244</v>
+        <v>75.33985817566804</v>
       </c>
       <c r="I25" t="n">
-        <v>8.660478444863566</v>
+        <v>8.696153298053911</v>
       </c>
       <c r="J25" t="n">
-        <v>1.699772800176782</v>
+        <v>1.69621597800523</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -1467,19 +1467,19 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>9.993961386968888</v>
+        <v>9.979624769461763</v>
       </c>
       <c r="E26" t="n">
-        <v>9.615141491698431</v>
+        <v>9.596153576510346</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3150876858970386</v>
+        <v>0.3126297736603003</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5926255127108753</v>
+        <v>0.5906381882959256</v>
       </c>
       <c r="H26" t="n">
-        <v>77.65468329743177</v>
+        <v>77.43904313154199</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1.029301682593235</v>
+        <v>1.029188065964594</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -1509,19 +1509,19 @@
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9.986908343094568</v>
       </c>
       <c r="E27" t="n">
-        <v>7.377498105298735</v>
+        <v>7.30321960900018</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3130723155660412</v>
+        <v>0.301299360015123</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3624350918176758</v>
+        <v>0.3622629762063053</v>
       </c>
       <c r="H27" t="n">
-        <v>77.27834680998167</v>
+        <v>76.19129467508793</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1.029253490903874</v>
+        <v>1.028901401443768</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -1551,19 +1551,19 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>9.911918960489093</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>5.662399865928845</v>
+        <v>5.568017431579672</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3101063132819616</v>
+        <v>0.2928299173150126</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2390230568343995</v>
+        <v>0.2376217926739152</v>
       </c>
       <c r="H28" t="n">
-        <v>76.73782305180139</v>
+        <v>75.06862185498507</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1.028955611524958</v>
+        <v>1.028837805069525</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -1593,19 +1593,19 @@
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9.992556710423202</v>
       </c>
       <c r="E29" t="n">
-        <v>4.719020885283882</v>
+        <v>4.790328335899439</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2963754209793126</v>
+        <v>0.3035682966179949</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1874248550106666</v>
+        <v>0.1880274365198054</v>
       </c>
       <c r="H29" t="n">
-        <v>75.1763391134927</v>
+        <v>75.90078527624199</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1.028867201792799</v>
+        <v>1.02897375172378</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -1635,19 +1635,19 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>9.983489342299752</v>
+        <v>9.938918079143928</v>
       </c>
       <c r="E30" t="n">
-        <v>8.682278123787668</v>
+        <v>8.593101974825442</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3637765591919478</v>
+        <v>0.3529110459049766</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4856263192620457</v>
+        <v>0.485547574640147</v>
       </c>
       <c r="H30" t="n">
-        <v>73.45854816961868</v>
+        <v>72.61017516879232</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1.047835130670388</v>
+        <v>1.047234721318602</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
@@ -1677,19 +1677,19 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>9.999870628537179</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>6.882210652134614</v>
+        <v>6.832540450238677</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3589518927818178</v>
+        <v>0.3511748551224521</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3228393039750759</v>
+        <v>0.3229115127259521</v>
       </c>
       <c r="H31" t="n">
-        <v>72.96639562965539</v>
+        <v>72.35061712592548</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1.047690279354309</v>
+        <v>1.047400822184946</v>
       </c>
       <c r="K31" t="b">
         <v>1</v>
@@ -1719,19 +1719,19 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>9.996780793875969</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>5.533374305743559</v>
+        <v>5.457754319562969</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3626509498328369</v>
+        <v>0.3539181438987336</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2263604351052843</v>
+        <v>0.2256430102728425</v>
       </c>
       <c r="H32" t="n">
-        <v>73.09157998092373</v>
+        <v>72.39505582547966</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1.047845388157872</v>
+        <v>1.04750011366614</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -1761,19 +1761,19 @@
         <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>9.979514109014959</v>
+        <v>9.991277707158803</v>
       </c>
       <c r="E33" t="n">
-        <v>4.555157166219643</v>
+        <v>4.589043577366641</v>
       </c>
       <c r="F33" t="n">
-        <v>0.344710112752074</v>
+        <v>0.3473696689809506</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1815935271487432</v>
+        <v>0.1815579390502898</v>
       </c>
       <c r="H33" t="n">
-        <v>71.44530552426433</v>
+        <v>71.68287662438209</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1.047164763935485</v>
+        <v>1.047269020384898</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -1803,19 +1803,19 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>9.996177147223333</v>
+        <v>9.998549929634308</v>
       </c>
       <c r="E34" t="n">
-        <v>8.400979470258177</v>
+        <v>8.425164497919537</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3731110544671281</v>
+        <v>0.3776686290972985</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4574714040354493</v>
+        <v>0.4575463285060781</v>
       </c>
       <c r="H34" t="n">
-        <v>71.25034607666964</v>
+        <v>71.57910980454916</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1.058103837268028</v>
+        <v>1.058321363156429</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -1845,19 +1845,19 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>9.988103622615212</v>
+        <v>9.905190651647297</v>
       </c>
       <c r="E35" t="n">
-        <v>6.669688946049781</v>
+        <v>6.665785266110943</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3649319884394652</v>
+        <v>0.3735663374665415</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3120041864563047</v>
+        <v>0.3130465044425254</v>
       </c>
       <c r="H35" t="n">
-        <v>70.50965873841449</v>
+        <v>71.12114311202437</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1.057786096784616</v>
+        <v>1.057748793781104</v>
       </c>
       <c r="K35" t="b">
         <v>1</v>
@@ -1890,16 +1890,16 @@
         <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>5.349261153194499</v>
+        <v>5.327398592163599</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3647286305390489</v>
+        <v>0.3622625201172933</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2216701254154075</v>
+        <v>0.2217817038534384</v>
       </c>
       <c r="H36" t="n">
-        <v>70.33778651268196</v>
+        <v>70.14177079771929</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1.057844143621523</v>
+        <v>1.05777331658024</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -1929,19 +1929,19 @@
         <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>9.998348917583206</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>4.607302349144194</v>
+        <v>4.673350750412598</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3710400723561143</v>
+        <v>0.3775388240804841</v>
       </c>
       <c r="G37" t="n">
-        <v>0.17772830745027</v>
+        <v>0.177831234190273</v>
       </c>
       <c r="H37" t="n">
-        <v>70.69197882563518</v>
+        <v>71.1926112222644</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1.058070930899865</v>
+        <v>1.058351352973757</v>
       </c>
       <c r="K37" t="b">
         <v>1</v>
@@ -1974,16 +1974,16 @@
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>8.15728590388847</v>
+        <v>8.182052620439235</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3871552166039902</v>
+        <v>0.3919874562978682</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4326970817608063</v>
+        <v>0.4328017263229895</v>
       </c>
       <c r="H38" t="n">
-        <v>69.15000366847231</v>
+        <v>69.47804945095285</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1.073008105893918</v>
+        <v>1.073207186663292</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -2013,19 +2013,19 @@
         <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>9.991773560106584</v>
+        <v>9.991376412223993</v>
       </c>
       <c r="E39" t="n">
-        <v>6.513420529157671</v>
+        <v>6.690258725587059</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3760020936909901</v>
+        <v>0.4013270237598456</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3013514131911016</v>
+        <v>0.3017630733577767</v>
       </c>
       <c r="H39" t="n">
-        <v>68.2382289944498</v>
+        <v>69.99394791970769</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1.072630269854054</v>
+        <v>1.073636561261876</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
@@ -2055,19 +2055,19 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9.993331625431704</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>5.417443337227986</v>
+        <v>5.298005675774391</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3948400253012215</v>
+        <v>0.3812106363241138</v>
       </c>
       <c r="G40" t="n">
-        <v>0.217523828455689</v>
+        <v>0.2170245351877565</v>
       </c>
       <c r="H40" t="n">
-        <v>69.44669963898355</v>
+        <v>68.48236318820392</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1.073343247910233</v>
+        <v>1.072835232221965</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
@@ -2097,19 +2097,19 @@
         <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>9.995584899016585</v>
       </c>
       <c r="E41" t="n">
-        <v>4.546045694898123</v>
+        <v>4.525881043599196</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3882886146593044</v>
+        <v>0.3869219612201075</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1725853292715248</v>
+        <v>0.1741968616688827</v>
       </c>
       <c r="H41" t="n">
-        <v>68.86841129124387</v>
+        <v>68.76546388087148</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1.073107866441083</v>
+        <v>1.07303405037782</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
@@ -2139,19 +2139,19 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>9.982284025876051</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>7.928715113741641</v>
+        <v>7.825907113126409</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4026596202768546</v>
+        <v>0.3812600625077391</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4099657984679262</v>
+        <v>0.4131051216635591</v>
       </c>
       <c r="H42" t="n">
-        <v>66.71133464160422</v>
+        <v>65.28734894051074</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1.095782840284635</v>
+        <v>1.09557420842688</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
@@ -2181,19 +2181,19 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>9.935539403639641</v>
       </c>
       <c r="E43" t="n">
-        <v>6.484343464747518</v>
+        <v>6.490224123233284</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4023793124259797</v>
+        <v>0.4098455131751815</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2897104572664461</v>
+        <v>0.2906727683779374</v>
       </c>
       <c r="H43" t="n">
-        <v>66.60976761931202</v>
+        <v>67.04620331341474</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>1.095916584242296</v>
+        <v>1.095801714359924</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
@@ -2223,19 +2223,19 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>9.999970701453091</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>5.240921287577926</v>
+        <v>5.271182190177195</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3960786441817501</v>
+        <v>0.3993808947961302</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2112181917407844</v>
+        <v>0.2111421313909393</v>
       </c>
       <c r="H44" t="n">
-        <v>66.07467465097457</v>
+        <v>66.29660584654972</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1.09576688897643</v>
+        <v>1.095868233736496</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
@@ -2265,19 +2265,19 @@
         <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>9.899075650183208</v>
       </c>
       <c r="E45" t="n">
-        <v>4.476255730134411</v>
+        <v>4.511758109183091</v>
       </c>
       <c r="F45" t="n">
-        <v>0.406496675278444</v>
+        <v>0.4149294178463168</v>
       </c>
       <c r="G45" t="n">
-        <v>0.164866985688664</v>
+        <v>0.1670328290923339</v>
       </c>
       <c r="H45" t="n">
-        <v>66.64384129910299</v>
+        <v>67.12682133174181</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1.096140422977215</v>
+        <v>1.095851519507687</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
@@ -2307,19 +2307,19 @@
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>9.712599832943557</v>
       </c>
       <c r="E46" t="n">
-        <v>7.696623465504347</v>
+        <v>7.510990810945947</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4063446213520773</v>
+        <v>0.417155946292156</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3873699288062462</v>
+        <v>0.3896084565161211</v>
       </c>
       <c r="H46" t="n">
-        <v>62.74229051732911</v>
+        <v>63.23193119798277</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1.135071733097295</v>
+        <v>1.132817735495171</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
@@ -2349,19 +2349,19 @@
         <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>9.906899480111097</v>
+        <v>9.91697533701028</v>
       </c>
       <c r="E47" t="n">
-        <v>6.432033232389816</v>
+        <v>6.320979898753474</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4317892826988117</v>
+        <v>0.4157716868440314</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2797520915868028</v>
+        <v>0.277849589030143</v>
       </c>
       <c r="H47" t="n">
-        <v>64.04806880777188</v>
+        <v>63.16846779160656</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1.134926020762822</v>
+        <v>1.134530988951689</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
@@ -2391,19 +2391,19 @@
         <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>9.851835144586508</v>
+        <v>10</v>
       </c>
       <c r="E48" t="n">
-        <v>5.112106094319983</v>
+        <v>5.182310683896417</v>
       </c>
       <c r="F48" t="n">
-        <v>0.411432739487922</v>
+        <v>0.4091107187405995</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2047464153679239</v>
+        <v>0.203316550222039</v>
       </c>
       <c r="H48" t="n">
-        <v>62.76392284040853</v>
+        <v>62.7066365584928</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1.134064457868286</v>
+        <v>1.135253367828725</v>
       </c>
       <c r="K48" t="b">
         <v>1</v>
@@ -2433,19 +2433,19 @@
         <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>9.976001845308813</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>4.263321922083071</v>
+        <v>4.184273518907238</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4155858466690455</v>
+        <v>0.4061685174169275</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1528164066645264</v>
+        <v>0.1527615266837753</v>
       </c>
       <c r="H49" t="n">
-        <v>62.9494226947822</v>
+        <v>62.37608432653674</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>1.135196634293737</v>
+        <v>1.135353222587472</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
@@ -2475,19 +2475,19 @@
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>9.999140430825339</v>
+        <v>9.998081583609824</v>
       </c>
       <c r="E50" t="n">
-        <v>7.524406591492188</v>
+        <v>7.503314734002147</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4147927370369681</v>
+        <v>0.411488924110392</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3609521577237418</v>
+        <v>0.3610816941158174</v>
       </c>
       <c r="H50" t="n">
-        <v>57.08489173065124</v>
+        <v>56.91812480295305</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1.218354888731473</v>
+        <v>1.218666459411536</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -2517,19 +2517,19 @@
         <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>9.986460996895824</v>
+        <v>9.988351596190059</v>
       </c>
       <c r="E51" t="n">
-        <v>6.172671534278422</v>
+        <v>6.223024844145552</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4105574700024307</v>
+        <v>0.4169439395140185</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2595297298774583</v>
+        <v>0.2590460610332494</v>
       </c>
       <c r="H51" t="n">
-        <v>56.77985173925678</v>
+        <v>57.10651345798993</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1.218871434855688</v>
+        <v>1.218346249858617</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
@@ -2562,16 +2562,16 @@
         <v>10</v>
       </c>
       <c r="E52" t="n">
-        <v>5.173207451816733</v>
+        <v>5.04878569468245</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4265262945502218</v>
+        <v>0.4126899809901396</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1866640615759435</v>
+        <v>0.1870422199344522</v>
       </c>
       <c r="H52" t="n">
-        <v>57.48057821185479</v>
+        <v>56.78148856722952</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1.218288923656427</v>
+        <v>1.219130242235689</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -2601,19 +2601,19 @@
         <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>9.99954025061748</v>
+        <v>9.961851619028851</v>
       </c>
       <c r="E53" t="n">
-        <v>4.082973869050263</v>
+        <v>4.076430047556464</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4347311919969728</v>
+        <v>0.4361734889628364</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1267086052292109</v>
+        <v>0.1270702709357717</v>
       </c>
       <c r="H53" t="n">
-        <v>57.71738937758505</v>
+        <v>57.77568437301741</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1.218469613600509</v>
+        <v>1.21798845263736</v>
       </c>
       <c r="K53" t="b">
         <v>1</v>
@@ -2643,19 +2643,19 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>9.997220441097443</v>
+        <v>9.906899652961233</v>
       </c>
       <c r="E54" t="n">
-        <v>7.317037550552269</v>
+        <v>7.255445380465333</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3953795559972031</v>
+        <v>0.3978441252454671</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3195901029421965</v>
+        <v>0.3200763097251352</v>
       </c>
       <c r="H54" t="n">
-        <v>43.38223757262983</v>
+        <v>43.49738624422451</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1.51011993010586</v>
+        <v>1.507071534259756</v>
       </c>
       <c r="K54" t="b">
         <v>1</v>
@@ -2685,19 +2685,19 @@
         <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>9.782442287364308</v>
+        <v>9.98717959292958</v>
       </c>
       <c r="E55" t="n">
-        <v>5.874646213991427</v>
+        <v>5.995091610019452</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3987141594674633</v>
+        <v>0.3944729801045825</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2222069388461854</v>
+        <v>0.2212253719183446</v>
       </c>
       <c r="H55" t="n">
-        <v>43.44973282143349</v>
+        <v>43.24668435346771</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1.505386300259821</v>
+        <v>1.511790944050425</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
@@ -2727,19 +2727,19 @@
         <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>9.934162995906943</v>
+        <v>9.989370188202738</v>
       </c>
       <c r="E56" t="n">
-        <v>4.738743824609441</v>
+        <v>4.772296821074846</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4069393974023864</v>
+        <v>0.4066773246866501</v>
       </c>
       <c r="G56" t="n">
-        <v>0.144755754450227</v>
+        <v>0.1444262488442998</v>
       </c>
       <c r="H56" t="n">
-        <v>43.55139744328304</v>
+        <v>43.52814537151974</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1.507720907029545</v>
+        <v>1.50892184845654</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
@@ -2769,19 +2769,19 @@
         <v>10</v>
       </c>
       <c r="D57" t="n">
-        <v>9.229123726436061</v>
+        <v>9.964938606729007</v>
       </c>
       <c r="E57" t="n">
-        <v>3.211553457767593</v>
+        <v>3.425215794348718</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4663433001857673</v>
+        <v>0.4419569762586705</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0877713042561095</v>
+        <v>0.08642891454325609</v>
       </c>
       <c r="H57" t="n">
-        <v>45.3259020817446</v>
+        <v>44.37158945619331</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1.477651954878132</v>
+        <v>1.500887142673699</v>
       </c>
       <c r="K57" t="b">
         <v>1</v>
@@ -2811,19 +2811,19 @@
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>9.99631347070215</v>
+        <v>9.925922901856239</v>
       </c>
       <c r="E58" t="n">
-        <v>7.318882486209912</v>
+        <v>7.125546163253421</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4999782667406912</v>
+        <v>0.480125035889797</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3556081791052068</v>
+        <v>0.3567522629549614</v>
       </c>
       <c r="H58" t="n">
-        <v>67.15165997856178</v>
+        <v>65.81986608628107</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1.046807181958469</v>
+        <v>1.045844306827123</v>
       </c>
       <c r="K58" t="b">
         <v>1</v>
@@ -2853,19 +2853,19 @@
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>9.977638672426428</v>
+        <v>9.996427475497564</v>
       </c>
       <c r="E59" t="n">
-        <v>6.182782106364865</v>
+        <v>6.109031524118048</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4976415817472307</v>
+        <v>0.4867660345185331</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2720564885705056</v>
+        <v>0.2715770794525316</v>
       </c>
       <c r="H59" t="n">
-        <v>66.93387904217469</v>
+        <v>66.2848999399292</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1.046649666986403</v>
+        <v>1.046291743050821</v>
       </c>
       <c r="K59" t="b">
         <v>1</v>
@@ -2898,16 +2898,16 @@
         <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>5.099835921835587</v>
+        <v>5.226264646306182</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4791089099987487</v>
+        <v>0.4922745597272649</v>
       </c>
       <c r="G60" t="n">
-        <v>0.213064094875261</v>
+        <v>0.2131988113912831</v>
       </c>
       <c r="H60" t="n">
-        <v>65.7211316716127</v>
+        <v>66.57091750403212</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1.046046746794953</v>
+        <v>1.046512961889965</v>
       </c>
       <c r="K60" t="b">
         <v>1</v>
@@ -2937,19 +2937,19 @@
         <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>9.996686645972513</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>4.54853148346593</v>
+        <v>4.597864399527374</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4824189412773205</v>
+        <v>0.4869873353107414</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1821101549503485</v>
+        <v>0.1818487589063037</v>
       </c>
       <c r="H61" t="n">
-        <v>65.87418283591352</v>
+        <v>66.17839704390454</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1.046149916537288</v>
+        <v>1.046316421741626</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
